--- a/artfynd/A 16369-2023 artfynd.xlsx
+++ b/artfynd/A 16369-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 16369-2023 artfynd.xlsx
+++ b/artfynd/A 16369-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96347325</v>
+        <v>96347331</v>
       </c>
       <c r="B2" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497006.1677831062</v>
+        <v>497072</v>
       </c>
       <c r="R2" t="n">
-        <v>7038461.753390134</v>
+        <v>7038515</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96347326</v>
+        <v>96347325</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497015.9773388632</v>
+        <v>497006</v>
       </c>
       <c r="R3" t="n">
-        <v>7038421.065343162</v>
+        <v>7038462</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,19 +847,9 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96347331</v>
+        <v>96347334</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497071.5688406107</v>
+        <v>497008</v>
       </c>
       <c r="R4" t="n">
-        <v>7038514.887345986</v>
+        <v>7038331</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,19 +948,9 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96347334</v>
+        <v>96347327</v>
       </c>
       <c r="B5" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497007.835857196</v>
+        <v>497038</v>
       </c>
       <c r="R5" t="n">
-        <v>7038331.220029721</v>
+        <v>7038487</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,19 +1049,9 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,43 +1079,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96347332</v>
+        <v>96347329</v>
       </c>
       <c r="B6" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>3286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1183,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497079.6258314375</v>
+        <v>497051</v>
       </c>
       <c r="R6" t="n">
-        <v>7038514.879961631</v>
+        <v>7038446</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,19 +1150,9 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,42 +1180,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96347327</v>
+        <v>96347333</v>
       </c>
       <c r="B7" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3215</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1299,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497037.9723181296</v>
+        <v>497106</v>
       </c>
       <c r="R7" t="n">
-        <v>7038487.203608151</v>
+        <v>7038455</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,28 +1252,17 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1372,42 +1281,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96347329</v>
+        <v>96347332</v>
       </c>
       <c r="B8" t="n">
-        <v>88886</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3286</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1415,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497050.4679218641</v>
+        <v>497079</v>
       </c>
       <c r="R8" t="n">
-        <v>7038446.513499271</v>
+        <v>7038515</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,19 +1353,9 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 16369-2023 artfynd.xlsx
+++ b/artfynd/A 16369-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96347331</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96347325</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96347334</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96347327</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96347329</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96347333</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1380,8 +1415,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96347332</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>